--- a/datafile/parking_data.xlsx
+++ b/datafile/parking_data.xlsx
@@ -460,11 +460,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>空闲</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+          <t>占用</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>皖AD02439</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-04-13 19:10:22</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -677,7 +685,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -983,6 +991,29 @@
         </is>
       </c>
       <c r="E12" t="inlineStr">
+        <is>
+          <t>在场</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>皖AD02439</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-04-13 19:10:22</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>P001</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>在场</t>
         </is>

--- a/datafile/parking_data.xlsx
+++ b/datafile/parking_data.xlsx
@@ -570,11 +570,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>空闲</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+          <t>占用</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>皖AD04248</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2026-04-13 21:50:47</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -685,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,6 +1022,29 @@
         </is>
       </c>
       <c r="E13" t="inlineStr">
+        <is>
+          <t>在场</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>皖AD04248</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-04-13 21:50:47</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>P006</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>在场</t>
         </is>
